--- a/Documentation/YASHART_Manual_Testing.xlsx
+++ b/Documentation/YASHART_Manual_Testing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\testing\YASHART-Manual-Testing_corrected\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\testing\YASHART-Manual-Testing\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ED3F50-C8F3-4F1A-A133-51C6808DBB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9955712-307C-48D9-93E1-97373C49A153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="605">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -570,9 +570,6 @@
     <t>Verify the phone link in the header</t>
   </si>
   <si>
-    <t>Latest Google Chrome installed; stable internet connection; home page opened. Do NOT send any WhatsApp message or place any call - only verify what opens.</t>
-  </si>
-  <si>
     <t>1. Note the phone number text in the header.
 2. Hover over it and read the link shown in the browser status bar.
 3. Click the phone link.
@@ -612,9 +609,6 @@
   </si>
   <si>
     <t>Expected heading: Our Products</t>
-  </si>
-  <si>
-    <t>'Catalogue' label and 'Our Products' heading are shown. Intro text reads: 'Browse our full range and request a custom quote for any product — bulk-friendly pricing and custom printing available.' No typos.</t>
   </si>
   <si>
     <t>TC_010</t>
@@ -1242,9 +1236,6 @@
     <t>Verify layout and usability on a mobile viewport</t>
   </si>
   <si>
-    <t>Chrome DevTools device toolbar or a real mobile phone available.</t>
-  </si>
-  <si>
     <t>1. Set the viewport size (or use the phone) and load the home page.
 2. Scroll through the whole page.
 3. Tap each filter and open one product page.
@@ -1544,9 +1535,6 @@
     <t>Project Details</t>
   </si>
   <si>
-    <t>Results by Module (auto-calculated)</t>
-  </si>
-  <si>
     <t>Project Name</t>
   </si>
   <si>
@@ -1574,33 +1562,18 @@
     <t>Testing Period</t>
   </si>
   <si>
-    <t>Fill in: start date to end date</t>
-  </si>
-  <si>
     <t>Testing Environment</t>
   </si>
   <si>
-    <t>Fill in: OS, browser versions, device/viewport used</t>
-  </si>
-  <si>
-    <t>Fill in</t>
-  </si>
-  <si>
     <t>Test Execution Metrics (auto-calculated)</t>
   </si>
   <si>
     <t>Total Test Cases</t>
   </si>
   <si>
-    <t>Counted from the Test Cases sheet</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>From Test Execution &gt; Status</t>
-  </si>
-  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -1610,33 +1583,18 @@
     <t>Executed</t>
   </si>
   <si>
-    <t>Passed + Failed + Blocked</t>
-  </si>
-  <si>
-    <t>Total - Executed</t>
-  </si>
-  <si>
     <t>Execution %</t>
   </si>
   <si>
-    <t>Executed / Total</t>
-  </si>
-  <si>
     <t>Pass % (of executed)</t>
   </si>
   <si>
-    <t>Passed / Executed</t>
-  </si>
-  <si>
     <t>Defect Metrics (auto-calculated)</t>
   </si>
   <si>
     <t>Total Defects</t>
   </si>
   <si>
-    <t>Counted from Bug ID column in Bug Reports</t>
-  </si>
-  <si>
     <t>Critical Defects</t>
   </si>
   <si>
@@ -1652,9 +1610,6 @@
     <t>Open Defects</t>
   </si>
   <si>
-    <t>Total minus Closed and Rejected</t>
-  </si>
-  <si>
     <t>Scope and Findings</t>
   </si>
   <si>
@@ -1664,37 +1619,22 @@
     <t>Home page, header navigation, product catalogue (21 products), category filter (All + 6), product detail pages, WhatsApp/phone enquiry links, contact section, responsive layout, browser compatibility, URL handling and content consistency of https://yashart.netlify.app/.</t>
   </si>
   <si>
-    <t>Planned scope - edit if the executed scope differs</t>
-  </si>
-  <si>
     <t>Testing Types</t>
   </si>
   <si>
     <t>Smoke, Sanity, Functional, UI, Usability, Responsive, Compatibility, Regression, Retesting (after a defect is fixed).</t>
   </si>
   <si>
-    <t>Planned - remove any type not actually performed</t>
-  </si>
-  <si>
     <t>Major Findings</t>
   </si>
   <si>
-    <t>Complete AFTER execution. Summarise real defects/observations only.</t>
-  </si>
-  <si>
     <t>Known Limitations</t>
   </si>
   <si>
     <t>Manual testing only. Live third-party site tested without requirements document. WhatsApp, phone and Instagram links verified only up to the point they open (no messages sent, no calls placed). Browser and device coverage limited to what was available to the tester. No performance, security or accessibility audit.</t>
   </si>
   <si>
-    <t>Planned limitations - review and edit after execution</t>
-  </si>
-  <si>
     <t>Overall Conclusion</t>
-  </si>
-  <si>
-    <t>Complete AFTER execution, based on the metrics above.</t>
   </si>
   <si>
     <t>HOW TO USE THIS WORKBOOK</t>
@@ -1796,6 +1736,269 @@
   </si>
   <si>
     <t>Valid URLs open the corresponding content correctly. An unknown URL is handled appropriately without displaying misleading product details or causing an application crash. Record the actual behaviour before deciding whether it constitutes a defect.</t>
+  </si>
+  <si>
+    <t>Windows 11</t>
+  </si>
+  <si>
+    <t>Microsoft Edge 155.0.4283.45 (64-bit)</t>
+  </si>
+  <si>
+    <t>Microsoft Edge 155.0.4283.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page is loaded successfully, Header, product catalogue and contact details are visible. </t>
+  </si>
+  <si>
+    <t>Siddhi Kamble</t>
+  </si>
+  <si>
+    <t>The header and navigation, Our Products catalogue with category filters and product cards, brand section with tagline, Contact section with working hours, and copyright line are all present and displayed correctly. No sections are missing, overlapping, or cut off.</t>
+  </si>
+  <si>
+    <t>Y' logo mark, 'YASHART' with 'Screen Printing' are visible, aligned, readable and not cropped or stretched.</t>
+  </si>
+  <si>
+    <t>Page scrolls to the 'Our Products' section; Address bar shows '#products'.</t>
+  </si>
+  <si>
+    <t>Page scrolls to the 'Contacts' section; Address bar shows '#contacts'.</t>
+  </si>
+  <si>
+    <t>Clicking triggers a call prompt. No error page.</t>
+  </si>
+  <si>
+    <t>Catalogue' label and 'Our Products' heading are shown. Intro text reads: 'Browse our full range and request a custom quote for any product — bulk-friendly pricing and custom printing available.' No typos.</t>
+  </si>
+  <si>
+    <t>The “Our Products” heading and introductory text are displayed correctly, with no spelling errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No duplicate or truncated products/text found</t>
+  </si>
+  <si>
+    <t>Every product card is readable without missing any information</t>
+  </si>
+  <si>
+    <t>Matching detail page opens and its heading / tab title equals the card name.</t>
+  </si>
+  <si>
+    <t>every product detail card opens its own url link, no broken url found.</t>
+  </si>
+  <si>
+    <t>"All" section 21 cards are displayed</t>
+  </si>
+  <si>
+    <t>All category's prdouct counts are perfect</t>
+  </si>
+  <si>
+    <t>"Disposable Items" section 4 Cards are displayed</t>
+  </si>
+  <si>
+    <t>"Wedding Cards" section 4 Cards are displayed</t>
+  </si>
+  <si>
+    <t>"Visitng Cards" section 4 Cards are displayed</t>
+  </si>
+  <si>
+    <t>"Stickers and Labels" section 3 Cards are displayed</t>
+  </si>
+  <si>
+    <t>"Hotel Parcel Container" section 3  Cards are displayed</t>
+  </si>
+  <si>
+    <t>"Carry Bags" section 3 Cards are displayed</t>
+  </si>
+  <si>
+    <t>Only the selected filter button appears active at any time, and it is clearly distinguishable from the others. Button text are readable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. After refreshing the page, the selected “Carry Bags” filter resets to “All”.
+2. After opening a product from the “Wedding Cards” category and clicking “Back to products”, the filter resets to “All”.
+3. After opening a product from the “Wedding Cards” category and using the browser Back button, the “Wedding Cards” section is displayed.
+</t>
+  </si>
+  <si>
+    <t>All information is perfectly done.</t>
+  </si>
+  <si>
+    <t>Name, subcategory, material and size are identical on the card and the detail page of every product.</t>
+  </si>
+  <si>
+    <t>Each badge is displayed according to the expected behaviour defined for that product, badge is consistent with the catalogue card.</t>
+  </si>
+  <si>
+    <t>User is taken to the home page with the product catalogue visible.</t>
+  </si>
+  <si>
+    <t>home page is shown correctly, with active filter.</t>
+  </si>
+  <si>
+    <t>tel:+919323574124 triggers</t>
+  </si>
+  <si>
+    <t>Same Number appears on all sections</t>
+  </si>
+  <si>
+    <t>Instagram opens the profile 'yashart_214'. No wrong Profile.</t>
+  </si>
+  <si>
+    <t>Email address is displayed correctly. Clicking opens the default mail client with To: yashart139@gmail.com.</t>
+  </si>
+  <si>
+    <t>Mozilla Firefox</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge installed; stable internet connection.</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge  installed; stable internet connection; home page opened.</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge installed; stable internet connection; home page opened. Do NOT send any WhatsApp message or place any call - only verify what opens.</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge  installed; stable internet connection; home page opened. Do NOT send any WhatsApp message or place any call - only verify what opens.</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge installed; stable internet connection; home page opened.</t>
+  </si>
+  <si>
+    <t>Latest Microsoft Edge  installed; stable internet connection.</t>
+  </si>
+  <si>
+    <t>LatestMicrosoft Edge  installed; stable internet connection; home page opened.</t>
+  </si>
+  <si>
+    <t>The page displays without horizontal scrolling. Text is readable, product cards stack vertically, and images are not distorted. However, the telephone icon and phone number are not visible in the mobile view, so the Call Now option is unavailable. Other header links, filters, and product links are usable.</t>
+  </si>
+  <si>
+    <t>The telephone number is visible at 1366×768 and 1920×1080, but it is not visible at 768×1024. The layout displays differently across the tested viewport sizes.</t>
+  </si>
+  <si>
+    <t>Microsoft Edge DevTools device toolbar or a real mobile phone available.</t>
+  </si>
+  <si>
+    <t>Microsoft Edge DevTools responsive mode available.</t>
+  </si>
+  <si>
+    <t>Google Chrome</t>
+  </si>
+  <si>
+    <t>The WhatsApp logo appears different on the home page compared to the three product detail pages. This visual inconsistency was observed across the pages. Other brand names, navigation labels, browser tab titles, URLs, headings, and descriptions should be recorded based on your actual observations.</t>
+  </si>
+  <si>
+    <t>Clicked the WhatsApp Quote button on all three product pages. WhatsApp opened with a pre-filled message displaying the complete product names correctly, including &amp;, / and -. No characters were missing or cut off.</t>
+  </si>
+  <si>
+    <t>Responsive layout was checked at viewport widths ranging from 320 px to 1440 px and at 1920 px. Header, category filters and product grid displayed correctly at all tested widths. No overlapping elements, missing content, truncated text or horizontal scrolling was observed.</t>
+  </si>
+  <si>
+    <t>Call Now option (telephone icon and phone number) is not visible in mobile view. Defect logged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Telephone number is not visible at 768×1024. Same responsive contact visibility defect observed at mobile and tablet widths.</t>
+  </si>
+  <si>
+    <t>WhatsApp logo is visually inconsistent between the home page and product detail pages. Defect logged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	BUG-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	BUG-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	BUG-003</t>
+  </si>
+  <si>
+    <t>Call Now option not visible on mobile and tablet views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Windows 11</t>
+  </si>
+  <si>
+    <t>YASHART website is open. Mobile and tablet viewport modes are available.</t>
+  </si>
+  <si>
+    <t>1. Open the YASHART home page. 2. Enable responsive mode in DevTools. 3. Set viewport to 360×640. 4. Check the header for the Call Now option. 5. Repeat at 390×844 and 768×1024.</t>
+  </si>
+  <si>
+    <t>Telephone icon and phone number should be visible and accessible at supported mobile and tablet viewport sizes.</t>
+  </si>
+  <si>
+    <t>Telephone icon and phone number are not visible at mobile viewport sizes (360×640 and 390×844) or tablet viewport size (768×1024). They are visible at desktop sizes (1366×768 and 1920×1080).</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Observed in TC_047 and TC_048. The Call Now option is available on desktop but missing on mobile and tablet views.</t>
+  </si>
+  <si>
+    <t>Telephone number not visible at tablet resolution</t>
+  </si>
+  <si>
+    <t>YASHART home page is open and browser responsive mode is available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	1. Open YASHART home page. 2. Enable responsive mode. 3. Set viewport to 768×1024. 4. Check the header for the telephone icon and phone number. 5. Compare with 1366×768 and 1920×1080.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Telephone icon and phone number should be visible and accessible at the tablet viewport size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telephone number is not visible at 768×1024. It is visible at 1366×768 and 1920×1080. </t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Observed during TC_048. Telephone number visibility differs across the tested viewport sizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	WhatsApp logo visually inconsistent across pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	YASHART home page and three product detail pages are accessible.</t>
+  </si>
+  <si>
+    <t>1. Open the YASHART home page. 2. Observe the WhatsApp logo. 3. Open Food Parcel Container 500 ml. 4. Observe its WhatsApp logo. 5. Repeat for Aluminium Foil Container 450 ml and Royal Gold Foil Wedding Card. 6. Compare the logos across all pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	WhatsApp logo should have a consistent appearance and design across the home page and all product detail pages.</t>
+  </si>
+  <si>
+    <t>WhatsApp logo displayed on the home page differs visually from the logo displayed on the three product detail pages.</t>
+  </si>
+  <si>
+    <t>Observed during TC_054. Visual inconsistency found between the home page and product detail pages.</t>
+  </si>
+  <si>
+    <t>25-Oct-2026 to 28-Oct-2026</t>
+  </si>
+  <si>
+    <t>Windows 11; Microsoft Edge 155.0.4283.45 (64-bit); Google Chrome; Desktop, Tablet and Mobile viewports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Siddhi Kamble</t>
+  </si>
+  <si>
+    <t>1. The Call Now option (telephone icon and phone number) was not visible in mobile view.
+2. The telephone number was not visible at the 768×1024 tablet viewport.
+3. The WhatsApp logo appeared visually inconsistent between the home page and product detail pages.</t>
+  </si>
+  <si>
+    <t>A total of 54 test cases were executed for the YASHART website. Out of these, 51 test cases passed and 3 failed, resulting in a pass percentage of 94.4%. Three defects were identified and recorded in the Bug Reports sheet. The main issues were related to telephone contact visibility across responsive viewport sizes and WhatsApp logo consistency across pages. Overall, the website performed as expected in most tested scenarios, with some UI and responsive issues requiring attention.</t>
+  </si>
+  <si>
+    <t>Results by Module</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +2009,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1860,8 +2063,35 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1892,6 +2122,18 @@
         <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1917,10 +2159,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1972,9 +2215,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1984,8 +2224,45 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
@@ -2214,6 +2491,187 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1477684</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>195356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3204882</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3231834</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F636FB23-00F5-D9E6-4B3D-4D9763CF53F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22014331" y="576356"/>
+          <a:ext cx="1727198" cy="3036478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>314139</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>182282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>4026543</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>3853703</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2374FAAD-B675-F63B-CE7F-9F938CAFB08E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20850786" y="3872753"/>
+          <a:ext cx="3712404" cy="3671421"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>525037</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>246991</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>2260406</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4115955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4550C7B-F991-3D1E-86A5-AAB4BED6B69F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21052855" y="8294173"/>
+          <a:ext cx="1735369" cy="3868964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>2544751</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>234828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>4374963</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4069773</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D394A8A1-22DE-E41C-D0DB-98A197F272C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23072569" y="8282010"/>
+          <a:ext cx="1830212" cy="3834945"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3034,7 +3492,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K55"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="57.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
@@ -3048,7 +3506,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
@@ -3083,7 +3541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
@@ -3097,7 +3555,7 @@
         <v>134</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>135</v>
+        <v>555</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>136</v>
@@ -3110,17 +3568,17 @@
       </c>
       <c r="I2" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A2,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A2,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v xml:space="preserve">Page is loaded successfully, Header, product catalogue and contact details are visible. </v>
       </c>
       <c r="J2" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A2,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A2,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>139</v>
       </c>
@@ -3134,7 +3592,7 @@
         <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>556</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>142</v>
@@ -3147,17 +3605,17 @@
       </c>
       <c r="I3" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A3,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A3,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>The header and navigation, Our Products catalogue with category filters and product cards, brand section with tagline, Contact section with working hours, and copyright line are all present and displayed correctly. No sections are missing, overlapping, or cut off.</v>
       </c>
       <c r="J3" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A3,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A3,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>145</v>
       </c>
@@ -3171,7 +3629,7 @@
         <v>146</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>141</v>
+        <v>556</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>147</v>
@@ -3184,17 +3642,17 @@
       </c>
       <c r="I4" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A4,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A4,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Y' logo mark, 'YASHART' with 'Screen Printing' are visible, aligned, readable and not cropped or stretched.</v>
       </c>
       <c r="J4" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A4,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A4,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>150</v>
       </c>
@@ -3221,17 +3679,17 @@
       </c>
       <c r="I5" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A5,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A5,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Page scrolls back to the top (home section). Address bar shows '#home'. No error or page break.</v>
       </c>
       <c r="J5" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A5,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A5,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>156</v>
       </c>
@@ -3258,17 +3716,17 @@
       </c>
       <c r="I6" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A6,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A6,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Page scrolls to the 'Our Products' section; Address bar shows '#products'.</v>
       </c>
       <c r="J6" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A6,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A6,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -3295,17 +3753,17 @@
       </c>
       <c r="I7" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A7,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A7,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Page scrolls to the 'Contacts' section; Address bar shows '#contacts'.</v>
       </c>
       <c r="J7" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A7,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A7,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>167</v>
       </c>
@@ -3319,32 +3777,32 @@
         <v>168</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="I8" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A8,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A8,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Clicking triggers a call prompt. No error page.</v>
       </c>
       <c r="J8" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A8,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A8,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
@@ -3353,35 +3811,35 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="I9" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A9,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A9,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>WhatsApp (web or app) opens a chat with +91 93235 74124 with the message 'Hi Yashart, I would like a quote.' pre-filled. The message is not sent automatically.</v>
       </c>
       <c r="J9" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A9,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A9,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -3393,32 +3851,32 @@
         <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>141</v>
+        <v>556</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>181</v>
+      <c r="H10" s="25" t="s">
+        <v>529</v>
       </c>
       <c r="I10" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A10,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A10,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>The “Our Products” heading and introductory text are displayed correctly, with no spelling errors.</v>
       </c>
       <c r="J10" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A10,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A10,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>32</v>
@@ -3427,35 +3885,35 @@
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="I11" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A11,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A11,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Exactly 21 product cards are displayed.</v>
       </c>
       <c r="J11" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A11,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A11,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
@@ -3464,35 +3922,35 @@
         <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="I12" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A12,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A12,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v xml:space="preserve"> No duplicate or truncated products/text found</v>
       </c>
       <c r="J12" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A12,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A12,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>36</v>
@@ -3501,35 +3959,35 @@
         <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="I13" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A13,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A13,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Every product card is readable without missing any information</v>
       </c>
       <c r="J13" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A13,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A13,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>40</v>
@@ -3538,35 +3996,35 @@
         <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="I14" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A14,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A14,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Matching detail page opens and its heading / tab title equals the card name.</v>
       </c>
       <c r="J14" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A14,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A14,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -3575,35 +4033,35 @@
         <v>29</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="I15" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A15,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A15,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>every product detail card opens its own url link, no broken url found.</v>
       </c>
       <c r="J15" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A15,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A15,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>48</v>
@@ -3612,35 +4070,35 @@
         <v>49</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>135</v>
+        <v>560</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I16" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A16,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A16,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"All" section 21 cards are displayed</v>
       </c>
       <c r="J16" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A16,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A16,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>52</v>
@@ -3649,35 +4107,35 @@
         <v>49</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="I17" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A17,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A17,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Disposable Items" section 4 Cards are displayed</v>
       </c>
       <c r="J17" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A17,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A17,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>52</v>
@@ -3686,35 +4144,35 @@
         <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A18,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A18,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Wedding Cards" section 4 Cards are displayed</v>
       </c>
       <c r="J18" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A18,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A18,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>52</v>
@@ -3723,35 +4181,35 @@
         <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="I19" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A19,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A19,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Visitng Cards" section 4 Cards are displayed</v>
       </c>
       <c r="J19" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A19,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A19,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>52</v>
@@ -3760,35 +4218,35 @@
         <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="I20" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A20,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A20,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Stickers and Labels" section 3 Cards are displayed</v>
       </c>
       <c r="J20" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A20,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A20,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>52</v>
@@ -3797,35 +4255,35 @@
         <v>49</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="I21" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A21,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A21,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Carry Bags" section 3 Cards are displayed</v>
       </c>
       <c r="J21" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A21,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A21,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>52</v>
@@ -3834,35 +4292,35 @@
         <v>49</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="I22" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A22,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A22,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>"Hotel Parcel Container" section 3  Cards are displayed</v>
       </c>
       <c r="J22" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A22,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A22,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="71.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>56</v>
@@ -3871,35 +4329,35 @@
         <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="I23" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A23,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A23,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All category's prdouct counts are perfect</v>
       </c>
       <c r="J23" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A23,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A23,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
@@ -3908,35 +4366,35 @@
         <v>49</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="I24" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A24,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A24,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Only the selected filter button appears active at any time, and it is clearly distinguishable from the others. Button text are readable.</v>
       </c>
       <c r="J24" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A24,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A24,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="112.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -3945,27 +4403,30 @@
         <v>49</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="H25" s="3" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="I25" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A25,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A25,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v xml:space="preserve">1. After refreshing the page, the selected “Carry Bags” filter resets to “All”.
+2. After opening a product from the “Wedding Cards” category and clicking “Back to products”, the filter resets to “All”.
+3. After opening a product from the “Wedding Cards” category and using the browser Back button, the “Wedding Cards” section is displayed.
+</v>
       </c>
       <c r="J25" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A25,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A25,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>14</v>
@@ -3973,7 +4434,7 @@
     </row>
     <row r="26" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>67</v>
@@ -3982,35 +4443,35 @@
         <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="I26" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A26,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A26,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J26" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A26,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A26,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -4019,35 +4480,35 @@
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="I27" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A27,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A27,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J27" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A27,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A27,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -4056,35 +4517,35 @@
         <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="I28" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A28,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A28,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J28" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A28,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A28,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>67</v>
@@ -4093,35 +4554,35 @@
         <v>68</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="I29" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A29,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A29,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J29" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A29,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A29,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>67</v>
@@ -4130,35 +4591,35 @@
         <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="I30" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A30,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A30,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J30" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A30,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A30,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>67</v>
@@ -4167,35 +4628,35 @@
         <v>68</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="I31" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A31,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A31,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J31" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A31,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A31,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>67</v>
@@ -4204,35 +4665,35 @@
         <v>68</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="I32" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A32,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A32,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All information is perfectly done.</v>
       </c>
       <c r="J32" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A32,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A32,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>71</v>
@@ -4241,35 +4702,35 @@
         <v>68</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="I33" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A33,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A33,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Name, subcategory, material and size are identical on the card and the detail page of every product.</v>
       </c>
       <c r="J33" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A33,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A33,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="77" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
@@ -4278,35 +4739,35 @@
         <v>68</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="I34" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A34,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A34,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Each badge is displayed according to the expected behaviour defined for that product, badge is consistent with the catalogue card.</v>
       </c>
       <c r="J34" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A34,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A34,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>78</v>
@@ -4315,35 +4776,35 @@
         <v>68</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="I35" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A35,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A35,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>User is taken to the home page with the product catalogue visible.</v>
       </c>
       <c r="J35" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A35,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A35,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
@@ -4352,35 +4813,35 @@
         <v>68</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="I36" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A36,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A36,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>home page is shown correctly, with active filter.</v>
       </c>
       <c r="J36" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A36,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A36,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>82</v>
@@ -4389,35 +4850,35 @@
         <v>68</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="I37" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A37,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A37,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Each link loads the home page; 'Products' and 'Contact' lead to the 'Our Products' and Contact sections respectively. No 404.</v>
       </c>
       <c r="J37" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A37,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A37,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>85</v>
@@ -4426,35 +4887,35 @@
         <v>86</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="I38" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A38,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A38,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>WhatsApp opens a chat with +91 93235 74124 with the message 'Hi, I am interested in a quote for Food Parcel Container 500 ml' pre-filled. Message is not sent automatically.</v>
       </c>
       <c r="J38" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A38,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A38,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>85</v>
@@ -4463,35 +4924,35 @@
         <v>86</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="I39" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A39,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A39,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Chat opens with +91 93235 74124 and the message 'Hi, I am interested in a quote for Royal Gold Foil Wedding Card' pre-filled.</v>
       </c>
       <c r="J39" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A39,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A39,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>85</v>
@@ -4500,35 +4961,35 @@
         <v>86</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="G40" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="I40" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A40,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A40,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>For every product the pre-filled message contains that product's exact name (no name from another product).</v>
       </c>
       <c r="J40" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A40,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A40,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>85</v>
@@ -4537,35 +4998,35 @@
         <v>86</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="I41" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A41,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A41,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Clicked the WhatsApp Quote button on all three product pages. WhatsApp opened with a pre-filled message displaying the complete product names correctly, including &amp;, / and -. No characters were missing or cut off.</v>
       </c>
       <c r="J41" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A41,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A41,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>89</v>
@@ -4574,35 +5035,35 @@
         <v>86</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="I42" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A42,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A42,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>tel:+919323574124 triggers</v>
       </c>
       <c r="J42" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A42,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A42,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>89</v>
@@ -4611,27 +5072,27 @@
         <v>86</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="I43" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A43,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A43,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Same Number appears on all sections</v>
       </c>
       <c r="J43" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A43,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A43,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>14</v>
@@ -4639,7 +5100,7 @@
     </row>
     <row r="44" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>92</v>
@@ -4648,35 +5109,35 @@
         <v>93</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="I44" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A44,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A44,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All four details are displayed exactly as in the test data, readable and without typos.</v>
       </c>
       <c r="J44" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A44,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A44,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="25" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>92</v>
@@ -4685,35 +5146,35 @@
         <v>93</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="I45" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A45,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A45,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Copyright line is displayed correctly at the bottom of the page.</v>
       </c>
       <c r="J45" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A45,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A45,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>97</v>
@@ -4725,32 +5186,32 @@
         <v>98</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>141</v>
+        <v>559</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="I46" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A46,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A46,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Instagram opens the profile 'yashart_214'. No wrong Profile.</v>
       </c>
       <c r="J46" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A46,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A46,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="50" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>100</v>
@@ -4762,32 +5223,32 @@
         <v>101</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>141</v>
+        <v>556</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="I47" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A47,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A47,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Email address is displayed correctly. Clicking opens the default mail client with To: yashart139@gmail.com.</v>
       </c>
       <c r="J47" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A47,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A47,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="75" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="84.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>103</v>
@@ -4796,35 +5257,35 @@
         <v>104</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="I48" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A48,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A48,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>The page displays without horizontal scrolling. Text is readable, product cards stack vertically, and images are not distorted. However, the telephone icon and phone number are not visible in the mobile view, so the Call Now option is unavailable. Other header links, filters, and product links are usable.</v>
       </c>
       <c r="J48" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A48,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A48,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>103</v>
@@ -4833,35 +5294,35 @@
         <v>104</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G49" s="27" t="s">
         <v>367</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="I49" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A49,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A49,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>The telephone number is visible at 1366×768 and 1920×1080, but it is not visible at 768×1024. The layout displays differently across the tested viewport sizes.</v>
       </c>
       <c r="J49" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A49,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A49,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>108</v>
@@ -4870,35 +5331,35 @@
         <v>104</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H50" s="27" t="s">
         <v>373</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="I50" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A50,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A50,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All steps behave the same as in Chrome. No layout, font or functional differences.</v>
       </c>
       <c r="J50" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A50,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A50,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
@@ -4907,35 +5368,35 @@
         <v>104</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>376</v>
+        <v>317</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>373</v>
       </c>
       <c r="I51" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A51,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A51,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>All steps behave the same as in Chrome. No layout, font or functional differences.</v>
       </c>
       <c r="J51" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A51,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A51,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="75" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>112</v>
@@ -4944,35 +5405,35 @@
         <v>104</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="I52" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A52,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A52,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Responsive layout was checked at viewport widths ranging from 320 px to 1440 px and at 1920 px. Header, category filters and product grid displayed correctly at all tested widths. No overlapping elements, missing content, truncated text or horizontal scrolling was observed.</v>
       </c>
       <c r="J52" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A52,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A52,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="57.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>116</v>
@@ -4981,35 +5442,35 @@
         <v>117</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
+      </c>
+      <c r="G53" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H53" s="27" t="s">
+        <v>386</v>
       </c>
       <c r="I53" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A53,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A53,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>A user-friendly 'not found' message or a redirect to the home page is shown. No blank page or raw technical error, and the user can get back to the site.</v>
       </c>
       <c r="J53" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A53,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A53,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="75" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="67" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>116</v>
@@ -5018,35 +5479,35 @@
         <v>117</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>538</v>
+        <v>517</v>
+      </c>
+      <c r="G54" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="H54" s="27" t="s">
+        <v>518</v>
       </c>
       <c r="I54" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A54,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A54,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Valid URLs open the corresponding content correctly. An unknown URL is handled appropriately without displaying misleading product details or causing an application crash. Record the actual behaviour before deciding whether it constitutes a defect.</v>
       </c>
       <c r="J54" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A54,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A54,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="75" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="84.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>121</v>
@@ -5055,27 +5516,27 @@
         <v>117</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="I55" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$G$2:$G$55,MATCH($A55,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$G$2:$G$55,MATCH($A55,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>The WhatsApp logo appears different on the home page compared to the three product detail pages. This visual inconsistency was observed across the pages. Other brand names, navigation labels, browser tab titles, URLs, headings, and descriptions should be recorded based on your actual observations.</v>
       </c>
       <c r="J55" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($A55,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($A55,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>76</v>
@@ -5105,21 +5566,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="23.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.7265625" customWidth="1"/>
+    <col min="7" max="7" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
@@ -5127,16 +5588,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>131</v>
@@ -5145,13 +5606,13 @@
         <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
@@ -5159,20 +5620,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A2,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="C2" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G2" s="7" t="s">
-        <v>403</v>
+        <v>522</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="125" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>139</v>
       </c>
@@ -5180,20 +5649,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A3,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G3" s="7" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>145</v>
       </c>
@@ -5201,20 +5678,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A4,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
-        <v>403</v>
+      <c r="C4" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>525</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>150</v>
       </c>
@@ -5222,20 +5707,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A5,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="C5" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G5" s="7" t="s">
-        <v>403</v>
+        <v>155</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>156</v>
       </c>
@@ -5243,20 +5736,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A6,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G6" s="7" t="s">
-        <v>403</v>
+        <v>526</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>162</v>
       </c>
@@ -5264,20 +5765,28 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A7,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="C7" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G7" s="7" t="s">
-        <v>403</v>
+        <v>527</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>167</v>
       </c>
@@ -5285,1008 +5794,1405 @@
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A8,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G8" s="7" t="s">
-        <v>403</v>
+        <v>528</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B9" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A9,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Header &amp; Navigation</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G9" s="7" t="s">
-        <v>403</v>
+        <v>176</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A10,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G10" s="7" t="s">
-        <v>403</v>
+        <v>530</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A11,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G11" s="7" t="s">
-        <v>403</v>
+        <v>184</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B12" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A12,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G12" s="7" t="s">
-        <v>403</v>
+        <v>531</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B13" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A13,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="C13" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G13" s="7" t="s">
-        <v>403</v>
+        <v>532</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B14" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A14,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="C14" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G14" s="7" t="s">
-        <v>403</v>
+        <v>533</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A15,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Catalogue</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="C15" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G15" s="7" t="s">
-        <v>403</v>
+        <v>534</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A16,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="C16" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G16" s="7" t="s">
-        <v>403</v>
+        <v>535</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B17" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A17,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G17" s="7" t="s">
-        <v>403</v>
+        <v>537</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B18" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A18,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G18" s="7" t="s">
-        <v>403</v>
+        <v>538</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B19" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A19,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="C19" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G19" s="7" t="s">
-        <v>403</v>
+        <v>539</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B20" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A20,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="C20" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G20" s="7" t="s">
-        <v>403</v>
+        <v>540</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B21" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A21,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="C21" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G21" s="7" t="s">
-        <v>403</v>
+        <v>542</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B22" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A22,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G22" s="7" t="s">
-        <v>403</v>
+        <v>541</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A23,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="C23" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G23" s="7" t="s">
-        <v>403</v>
+        <v>536</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="75" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B24" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A24,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="C24" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G24" s="7" t="s">
-        <v>403</v>
+        <v>543</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="187.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B25" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A25,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Category Filter</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="C25" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G25" s="7" t="s">
-        <v>403</v>
+        <v>544</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A26,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="C26" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G26" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A27,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="C27" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G27" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B28" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A28,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="C28" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G28" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B29" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A29,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="C29" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G29" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B30" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A30,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G30" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B31" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A31,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="C31" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G31" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B32" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A32,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="C32" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G32" s="7" t="s">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B33" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A33,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="C33" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G33" s="7" t="s">
-        <v>403</v>
+        <v>546</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B34" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A34,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="C34" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G34" s="7" t="s">
-        <v>403</v>
+        <v>547</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B35" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A35,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="C35" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G35" s="7" t="s">
-        <v>403</v>
+        <v>548</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B36" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A36,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="C36" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G36" s="7" t="s">
-        <v>403</v>
+        <v>549</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B37" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A37,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Product Detail</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="C37" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G37" s="7" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B38" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A38,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="C38" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G38" s="7" t="s">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B39" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A39,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="C39" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G39" s="7" t="s">
-        <v>403</v>
+        <v>318</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I39" s="8"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B40" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A40,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="C40" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G40" s="7" t="s">
-        <v>403</v>
+        <v>324</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I40" s="8"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="112.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B41" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A41,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
+      <c r="C41" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G41" s="7" t="s">
-        <v>403</v>
+        <v>568</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I41" s="8"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B42" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A42,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7" t="s">
-        <v>403</v>
+      <c r="C42" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>550</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="25" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B43" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A43,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Enquiry Links</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="C43" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G43" s="7" t="s">
-        <v>403</v>
+        <v>551</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I43" s="8"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B44" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A44,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Contact &amp; Footer</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="C44" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G44" s="7" t="s">
-        <v>403</v>
+        <v>344</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B45" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A45,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Contact &amp; Footer</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="C45" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G45" s="7" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B46" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A46,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Contact &amp; Footer</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="C46" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G46" s="7" t="s">
-        <v>403</v>
+        <v>552</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B47" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A47,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Contact &amp; Footer</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
+      <c r="C47" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G47" s="7" t="s">
-        <v>403</v>
+        <v>553</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="150" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B48" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A48,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Responsive &amp; Compatibility</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="C48" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G48" s="7" t="s">
-        <v>403</v>
+        <v>562</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="7"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="125" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B49" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A49,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Responsive &amp; Compatibility</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="7"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C49" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>563</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B50" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A50,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Responsive &amp; Compatibility</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7" t="s">
-        <v>403</v>
+      <c r="C50" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>373</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="50" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B51" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A51,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Responsive &amp; Compatibility</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7" t="s">
-        <v>403</v>
+      <c r="C51" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>373</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="137.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B52" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A52,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>Responsive &amp; Compatibility</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="C52" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>566</v>
+      </c>
       <c r="G52" s="7" t="s">
-        <v>403</v>
+        <v>569</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="75" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B53" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A53,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>URL Handling &amp; Usability</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7" t="s">
-        <v>403</v>
+      <c r="C53" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>386</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="137.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B54" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A54,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>URL Handling &amp; Usability</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7" t="s">
-        <v>403</v>
+      <c r="C54" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>518</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" ht="150" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B55" s="5" t="str">
         <f>IFERROR(INDEX('Test Cases'!$C$2:$C$55,MATCH($A55,'Test Cases'!$A$2:$A$55,0)),"")</f>
         <v>URL Handling &amp; Usability</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7" t="s">
-        <v>403</v>
+      <c r="C55" s="6">
+        <v>46320</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="G55" s="28" t="s">
+        <v>567</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="7"/>
+        <v>458</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>572</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J55" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H2:H55">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Pass"</formula>
@@ -6311,6 +7217,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G42" r:id="rId1" xr:uid="{80A4B5D5-ED53-4463-877C-8D93C26E0EA3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -6321,42 +7230,45 @@
   <dimension ref="A1:P101"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="9" width="38" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="16" width="30" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.1796875" customWidth="1"/>
+    <col min="7" max="7" width="58.26953125" customWidth="1"/>
+    <col min="8" max="8" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="65.26953125" customWidth="1"/>
+    <col min="16" max="16" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>130</v>
@@ -6365,7 +7277,7 @@
         <v>131</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>3</v>
@@ -6374,71 +7286,161 @@
         <v>132</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="9"/>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="260.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>578</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="N2" s="9">
+        <v>46320</v>
+      </c>
       <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="9"/>
+      <c r="P2" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="343" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="N3" s="9">
+        <v>46320</v>
+      </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="9"/>
+      <c r="P3" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="341.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E4" t="s">
+        <v>566</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="N4" s="9">
+        <v>46320</v>
+      </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
@@ -8188,6 +9190,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P101" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C2:C101" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Header &amp; Navigation,Product Catalogue,Category Filter,Product Detail,Enquiry Links,Contact &amp; Footer,Responsive &amp; Compatibility,URL Handling &amp; Usability"</formula1>
@@ -8208,6 +9211,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8227,10 +9231,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -8242,18 +9246,18 @@
         <v>125</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
@@ -8266,7 +9270,7 @@
       </c>
       <c r="F2" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E2,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E2,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E2,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E2,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8275,10 +9279,10 @@
     </row>
     <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
@@ -8291,7 +9295,7 @@
       </c>
       <c r="F3" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E3,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E3,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E3,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E3,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8300,10 +9304,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -8316,7 +9320,7 @@
       </c>
       <c r="F4" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E4,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E4,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E4,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E4,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8325,10 +9329,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
@@ -8341,7 +9345,7 @@
       </c>
       <c r="F5" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E5,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E5,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E5,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E5,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8350,10 +9354,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -8366,7 +9370,7 @@
       </c>
       <c r="F6" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E6,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E6,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E6,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E6,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8375,10 +9379,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
@@ -8391,7 +9395,7 @@
       </c>
       <c r="F7" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E7,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E7,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E7,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E7,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8400,10 +9404,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
@@ -8416,7 +9420,7 @@
       </c>
       <c r="F8" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E8,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E8,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G8" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E8,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E8,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8425,10 +9429,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
@@ -8437,11 +9441,11 @@
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F9" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E9,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E9,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E9,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E9,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8450,10 +9454,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>29</v>
@@ -8462,11 +9466,11 @@
         <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F10" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E10,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E10,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E10,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E10,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8475,10 +9479,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>29</v>
@@ -8487,11 +9491,11 @@
         <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F11" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E11,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E11,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E11,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E11,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8500,10 +9504,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>29</v>
@@ -8512,11 +9516,11 @@
         <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F12" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E12,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E12,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E12,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E12,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8525,10 +9529,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>29</v>
@@ -8537,11 +9541,11 @@
         <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F13" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E13,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E13,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E13,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E13,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8550,10 +9554,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>29</v>
@@ -8562,11 +9566,11 @@
         <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F14" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E14,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E14,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E14,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E14,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8575,10 +9579,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>29</v>
@@ -8587,11 +9591,11 @@
         <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F15" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E15,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E15,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E15,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E15,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8600,10 +9604,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
@@ -8612,11 +9616,11 @@
         <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F16" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E16,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E16,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E16,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E16,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8625,10 +9629,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>49</v>
@@ -8637,11 +9641,11 @@
         <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F17" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E17,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E17,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G17" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E17,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E17,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8650,10 +9654,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>49</v>
@@ -8662,11 +9666,11 @@
         <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F18" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E18,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E18,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E18,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E18,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8675,10 +9679,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>49</v>
@@ -8687,11 +9691,11 @@
         <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F19" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E19,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E19,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E19,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E19,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8700,10 +9704,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>49</v>
@@ -8712,11 +9716,11 @@
         <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F20" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E20,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E20,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E20,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E20,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8725,10 +9729,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>49</v>
@@ -8737,11 +9741,11 @@
         <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F21" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E21,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E21,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E21,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E21,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8750,10 +9754,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>49</v>
@@ -8762,11 +9766,11 @@
         <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F22" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E22,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E22,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E22,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E22,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8775,10 +9779,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>49</v>
@@ -8787,11 +9791,11 @@
         <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F23" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E23,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E23,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E23,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E23,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8800,10 +9804,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>49</v>
@@ -8812,11 +9816,11 @@
         <v>60</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F24" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E24,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E24,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E24,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E24,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8825,10 +9829,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>49</v>
@@ -8837,11 +9841,11 @@
         <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F25" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E25,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E25,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G25" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E25,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E25,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8850,10 +9854,10 @@
     </row>
     <row r="26" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>68</v>
@@ -8862,11 +9866,11 @@
         <v>67</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F26" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E26,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E26,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G26" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E26,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E26,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8875,10 +9879,10 @@
     </row>
     <row r="27" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>68</v>
@@ -8887,11 +9891,11 @@
         <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F27" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E27,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E27,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G27" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E27,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E27,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8900,10 +9904,10 @@
     </row>
     <row r="28" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>68</v>
@@ -8912,11 +9916,11 @@
         <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F28" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E28,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E28,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G28" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E28,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E28,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8925,10 +9929,10 @@
     </row>
     <row r="29" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>68</v>
@@ -8937,11 +9941,11 @@
         <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F29" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E29,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E29,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G29" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E29,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E29,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8950,10 +9954,10 @@
     </row>
     <row r="30" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>68</v>
@@ -8962,11 +9966,11 @@
         <v>67</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F30" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E30,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E30,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G30" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E30,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E30,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -8975,10 +9979,10 @@
     </row>
     <row r="31" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>68</v>
@@ -8987,11 +9991,11 @@
         <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F31" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E31,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E31,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G31" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E31,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E31,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9000,10 +10004,10 @@
     </row>
     <row r="32" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>68</v>
@@ -9012,11 +10016,11 @@
         <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F32" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E32,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E32,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G32" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E32,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E32,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9025,10 +10029,10 @@
     </row>
     <row r="33" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>68</v>
@@ -9037,11 +10041,11 @@
         <v>71</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F33" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E33,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E33,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E33,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E33,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9050,10 +10054,10 @@
     </row>
     <row r="34" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>68</v>
@@ -9062,11 +10066,11 @@
         <v>74</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F34" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E34,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E34,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G34" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E34,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E34,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9075,10 +10079,10 @@
     </row>
     <row r="35" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>68</v>
@@ -9087,11 +10091,11 @@
         <v>78</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F35" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E35,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E35,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E35,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E35,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9100,10 +10104,10 @@
     </row>
     <row r="36" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>68</v>
@@ -9112,11 +10116,11 @@
         <v>78</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F36" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E36,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E36,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G36" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E36,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E36,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9125,10 +10129,10 @@
     </row>
     <row r="37" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>68</v>
@@ -9137,11 +10141,11 @@
         <v>82</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F37" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E37,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E37,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G37" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E37,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E37,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9150,10 +10154,10 @@
     </row>
     <row r="38" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>86</v>
@@ -9162,11 +10166,11 @@
         <v>85</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F38" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E38,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E38,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G38" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E38,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E38,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9175,10 +10179,10 @@
     </row>
     <row r="39" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>86</v>
@@ -9187,11 +10191,11 @@
         <v>85</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F39" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E39,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E39,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G39" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E39,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E39,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9200,10 +10204,10 @@
     </row>
     <row r="40" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>86</v>
@@ -9212,11 +10216,11 @@
         <v>85</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F40" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E40,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E40,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G40" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E40,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E40,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9225,10 +10229,10 @@
     </row>
     <row r="41" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>86</v>
@@ -9237,11 +10241,11 @@
         <v>85</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F41" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E41,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E41,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G41" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E41,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E41,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9250,10 +10254,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>86</v>
@@ -9262,11 +10266,11 @@
         <v>89</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F42" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E42,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E42,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G42" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E42,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E42,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9275,10 +10279,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>86</v>
@@ -9287,11 +10291,11 @@
         <v>89</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F43" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E43,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E43,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G43" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E43,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E43,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9300,10 +10304,10 @@
     </row>
     <row r="44" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>93</v>
@@ -9312,11 +10316,11 @@
         <v>92</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F44" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E44,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E44,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G44" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E44,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E44,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9325,10 +10329,10 @@
     </row>
     <row r="45" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>93</v>
@@ -9337,11 +10341,11 @@
         <v>92</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F45" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E45,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E45,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G45" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E45,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E45,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9350,10 +10354,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>93</v>
@@ -9362,11 +10366,11 @@
         <v>97</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F46" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E46,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E46,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G46" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E46,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E46,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9375,10 +10379,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>93</v>
@@ -9387,11 +10391,11 @@
         <v>100</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F47" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E47,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E47,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G47" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E47,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E47,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9400,10 +10404,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>104</v>
@@ -9412,23 +10416,23 @@
         <v>103</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F48" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E48,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E48,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="G48" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E48,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E48,'Test Execution'!$A$2:$A$55,0))),"")</f>
-        <v/>
+        <v xml:space="preserve">	BUG-001</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>104</v>
@@ -9437,23 +10441,23 @@
         <v>103</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F49" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E49,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E49,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="G49" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E49,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E49,'Test Execution'!$A$2:$A$55,0))),"")</f>
-        <v/>
+        <v xml:space="preserve">	BUG-002</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>104</v>
@@ -9462,11 +10466,11 @@
         <v>108</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F50" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E50,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E50,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G50" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E50,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E50,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9475,10 +10479,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>104</v>
@@ -9487,11 +10491,11 @@
         <v>108</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F51" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E51,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E51,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G51" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E51,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E51,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9500,10 +10504,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>104</v>
@@ -9512,11 +10516,11 @@
         <v>112</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F52" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E52,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E52,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G52" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E52,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E52,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9525,10 +10529,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>117</v>
@@ -9537,11 +10541,11 @@
         <v>116</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F53" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E53,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E53,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G53" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E53,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E53,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9550,10 +10554,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>117</v>
@@ -9562,11 +10566,11 @@
         <v>116</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F54" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E54,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E54,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
       <c r="G54" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E54,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E54,'Test Execution'!$A$2:$A$55,0))),"")</f>
@@ -9575,10 +10579,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>117</v>
@@ -9587,20 +10591,20 @@
         <v>121</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F55" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$H$2:$H$55,MATCH($E55,'Test Execution'!$A$2:$A$55,0))="","Not Executed",INDEX('Test Execution'!$H$2:$H$55,MATCH($E55,'Test Execution'!$A$2:$A$55,0))),"Not Executed")</f>
-        <v>Not Executed</v>
+        <v>Fail</v>
       </c>
       <c r="G55" s="4" t="str">
         <f>IFERROR(IF(INDEX('Test Execution'!$I$2:$I$55,MATCH($E55,'Test Execution'!$A$2:$A$55,0))="","",INDEX('Test Execution'!$I$2:$I$55,MATCH($E55,'Test Execution'!$A$2:$A$55,0))),"")</f>
-        <v/>
+        <v xml:space="preserve">	BUG-003</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -9631,7 +10635,7 @@
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="3" width="4.08984375" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="10" width="13" customWidth="1"/>
@@ -9639,54 +10643,51 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
       <c r="E3" s="14" t="s">
-        <v>457</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C4" s="16"/>
+        <v>455</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C5" s="16"/>
+        <v>461</v>
+      </c>
       <c r="E5" s="17" t="s">
         <v>7</v>
       </c>
@@ -9696,7 +10697,7 @@
       </c>
       <c r="G5" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E5,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H5" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E5,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9708,16 +10709,15 @@
       </c>
       <c r="J5" s="18">
         <f t="shared" ref="J5:J12" si="0">F5-G5-H5-I5</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="16" t="s">
-        <v>467</v>
+        <v>462</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>599</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>29</v>
@@ -9728,7 +10728,7 @@
       </c>
       <c r="G6" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E6,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E6,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9740,16 +10740,15 @@
       </c>
       <c r="J6" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="16" t="s">
-        <v>469</v>
+        <v>463</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>600</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>49</v>
@@ -9760,7 +10759,7 @@
       </c>
       <c r="G7" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E7,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E7,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9772,16 +10771,15 @@
       </c>
       <c r="J7" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="16" t="s">
-        <v>470</v>
+        <v>395</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>601</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>68</v>
@@ -9792,7 +10790,7 @@
       </c>
       <c r="G8" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E8,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H8" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E8,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9804,7 +10802,7 @@
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -9817,7 +10815,7 @@
       </c>
       <c r="G9" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E9,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E9,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9829,15 +10827,14 @@
       </c>
       <c r="J9" s="18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
       <c r="E10" s="17" t="s">
         <v>93</v>
       </c>
@@ -9847,7 +10844,7 @@
       </c>
       <c r="G10" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E10,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E10,'Test Execution'!$H$2:$H$55,"Fail")</f>
@@ -9859,19 +10856,16 @@
       </c>
       <c r="J10" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="B11" s="5">
+        <v>465</v>
+      </c>
+      <c r="B11" s="34">
         <f>COUNTA('Test Cases'!$A$2:$A$55)</f>
         <v>54</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>473</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>104</v>
@@ -9882,11 +10876,11 @@
       </c>
       <c r="G11" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E11,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E11,'Test Execution'!$H$2:$H$55,"Fail")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E11,'Test Execution'!$H$2:$H$55,"Blocked")</f>
@@ -9894,19 +10888,16 @@
       </c>
       <c r="J11" s="18">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="B12" s="5">
+        <v>466</v>
+      </c>
+      <c r="B12" s="34">
         <f>COUNTIF('Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>475</v>
+        <v>51</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>117</v>
@@ -9917,11 +10908,11 @@
       </c>
       <c r="G12" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E12,'Test Execution'!$H$2:$H$55,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E12,'Test Execution'!$H$2:$H$55,"Fail")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="18">
         <f>COUNTIFS('Test Execution'!$B$2:$B$55,$E12,'Test Execution'!$H$2:$H$55,"Blocked")</f>
@@ -9929,20 +10920,19 @@
       </c>
       <c r="J12" s="18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="B13" s="5">
+        <v>467</v>
+      </c>
+      <c r="B13" s="34">
         <f>COUNTIF('Test Execution'!$H$2:$H$55,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16"/>
+        <v>3</v>
+      </c>
       <c r="E13" s="19" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="F13" s="20">
         <f>SUM(F5:F12)</f>
@@ -9950,11 +10940,11 @@
       </c>
       <c r="G13" s="20">
         <f>SUM(G5:G12)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H13" s="20">
         <f>SUM(H5:H12)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="20">
         <f>SUM(I5:I12)</f>
@@ -9962,195 +10952,163 @@
       </c>
       <c r="J13" s="20">
         <f>SUM(J5:J12)</f>
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="B14" s="5">
+        <v>459</v>
+      </c>
+      <c r="B14" s="34">
         <f>COUNTIF('Test Execution'!$H$2:$H$55,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="C14" s="16"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="B15" s="5">
+        <v>469</v>
+      </c>
+      <c r="B15" s="34">
         <f>B12+B13+B14</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>479</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="B16" s="5">
+        <v>400</v>
+      </c>
+      <c r="B16" s="34">
         <f>B11-B15</f>
-        <v>54</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="B17" s="21">
+        <v>470</v>
+      </c>
+      <c r="B17" s="35">
         <f>IF(B11=0,0,B15/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>482</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>483</v>
-      </c>
-      <c r="B18" s="21">
+        <v>471</v>
+      </c>
+      <c r="B18" s="35">
         <f>IF(B15=0,0,B12/B15)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>484</v>
+        <v>0.94444444444444442</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="B21" s="5">
+        <v>473</v>
+      </c>
+      <c r="B21" s="34">
         <f>COUNTA('Bug Reports'!$A$2:$A$101)</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>487</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="B22" s="5">
+        <v>474</v>
+      </c>
+      <c r="B22" s="34">
         <f>COUNTIF('Bug Reports'!$J$2:$J$101,"Critical")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="16"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="B23" s="5">
+        <v>475</v>
+      </c>
+      <c r="B23" s="34">
         <f>COUNTIF('Bug Reports'!$J$2:$J$101,"High")</f>
         <v>0</v>
       </c>
-      <c r="C23" s="16"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="B24" s="5">
+        <v>476</v>
+      </c>
+      <c r="B24" s="34">
         <f>COUNTIF('Bug Reports'!$J$2:$J$101,"Medium")</f>
         <v>0</v>
       </c>
-      <c r="C24" s="16"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="B25" s="5">
+        <v>477</v>
+      </c>
+      <c r="B25" s="34">
         <f>COUNTIF('Bug Reports'!$J$2:$J$101,"Low")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>492</v>
-      </c>
-      <c r="B26" s="5">
+        <v>478</v>
+      </c>
+      <c r="B26" s="34">
         <f>B21-COUNTIF('Bug Reports'!$L$2:$L$101,"Closed")-COUNTIF('Bug Reports'!$L$2:$L$101,"Rejected")</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>493</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
     </row>
     <row r="29" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>483</v>
+      </c>
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="1:3" ht="91" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="16" t="s">
-        <v>502</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="1:3" ht="110.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="16" t="s">
-        <v>507</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>603</v>
+      </c>
+      <c r="C33" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10168,97 +11126,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>508</v>
-      </c>
-      <c r="B1" s="23"/>
+      <c r="A1" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="22"/>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
-        <v>509</v>
+      <c r="A2" s="23" t="s">
+        <v>489</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
